--- a/data/trans_orig/IP74A1_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP74A1_2023-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Adulto según si ha resuelto la hipoteca en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Adultos según si tienen resuelto el retraso en los pagos de la hipoteca en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2102,7 +2102,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4798</t>
+          <t>4976</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>67,51%</t>
+          <t>70,01%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2172,7 +2172,7 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>16155</t>
+          <t>16388</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>86,13%</t>
+          <t>87,38%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2220,7 +2220,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2309</t>
+          <t>2131</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2235,7 +2235,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>29,99%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2290,7 +2290,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2601</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2305,7 +2305,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>12,62%</t>
         </is>
       </c>
     </row>
